--- a/信息工程系_外聘_见习岗_人名单20260316.xlsx
+++ b/信息工程系_外聘_见习岗_人名单20260316.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="24000" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>序号</t>
   </si>
@@ -171,6 +171,12 @@
   </si>
   <si>
     <t>陈思文</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>关天昊</t>
   </si>
 </sst>
 </file>
@@ -815,7 +821,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -824,6 +830,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1353,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1625,6 +1634,17 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
